--- a/astro-site/public/dl/haccp-templates/01-food-temperature-log.xlsx
+++ b/astro-site/public/dl/haccp-templates/01-food-temperature-log.xlsx
@@ -786,7 +786,7 @@
     <row r="16">
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>▸ Freezers: 0 °F (-18 °C) or below. There is NO lower limit: a chest freezer at -15 °F or a blast chiller at -22 °F is compliant.</t>
+          <t>▸ Freezers: 0 °F (-18 °C) or below. There is NO lower limit: a chest freezer at -15 °F or a blast freezer at -22 °F is compliant.</t>
         </is>
       </c>
     </row>
